--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9375" windowHeight="8655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerNumericConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>c</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>经验值</t>
+  </si>
+  <si>
+    <t>关卡冒险状态</t>
+  </si>
+  <si>
+    <t>关卡开始冒险的时间</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H22"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1504,6 +1510,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="3:8">
+      <c r="C23" s="3">
+        <v>3010</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8">
+      <c r="C24" s="3">
+        <v>3011</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerNumericConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>c</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>关卡开始冒险的时间</t>
+  </si>
+  <si>
+    <t>是否存活</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H24"/>
+  <dimension ref="B2:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1550,6 +1553,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="3:8">
+      <c r="C25" s="3">
+        <v>3012</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerNumericConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>c</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>护甲追加</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>最大法力值</t>
   </si>
   <si>
     <t>#直接使用没有加成的属性</t>
@@ -846,7 +852,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1125,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H25"/>
+  <dimension ref="B2:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1327,55 +1333,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="3:8">
+      <c r="C13" s="3">
+        <v>1017</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="3:8">
       <c r="C14" s="3">
-        <v>3001</v>
+        <v>1018</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8">
-      <c r="C15" s="3">
-        <v>3002</v>
-      </c>
-      <c r="D15" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1</v>
-      </c>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" spans="3:8">
       <c r="C16" s="3">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>25</v>
@@ -1395,7 +1401,7 @@
     </row>
     <row r="17" spans="3:8">
       <c r="C17" s="3">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>26</v>
@@ -1415,53 +1421,53 @@
     </row>
     <row r="18" spans="3:8">
       <c r="C18" s="3">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="3:8">
       <c r="C19" s="3">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3">
-        <v>5</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="3:8">
       <c r="C20" s="3">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1475,33 +1481,33 @@
     </row>
     <row r="21" spans="3:8">
       <c r="C21" s="3">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
+        <v>5</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:8">
       <c r="C22" s="3">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1515,7 +1521,7 @@
     </row>
     <row r="23" spans="3:8">
       <c r="C23" s="3">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>32</v>
@@ -1535,7 +1541,7 @@
     </row>
     <row r="24" spans="3:8">
       <c r="C24" s="3">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>33</v>
@@ -1555,7 +1561,7 @@
     </row>
     <row r="25" spans="3:8">
       <c r="C25" s="3">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>34</v>
@@ -1570,6 +1576,46 @@
         <v>0</v>
       </c>
       <c r="H25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8">
+      <c r="C26" s="3">
+        <v>3011</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8">
+      <c r="C27" s="3">
+        <v>3012</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>c</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>是否存活</t>
+  </si>
+  <si>
+    <t>濒死状态</t>
   </si>
 </sst>
 </file>
@@ -150,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +172,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF57A64A"/>
+      <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -640,137 +649,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -783,6 +792,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1131,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H27"/>
+  <dimension ref="B2:H28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1341,10 +1351,10 @@
         <v>22</v>
       </c>
       <c r="E13" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
@@ -1361,10 +1371,10 @@
         <v>23</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1616,6 +1626,26 @@
         <v>0</v>
       </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8">
+      <c r="C28" s="3">
+        <v>3013</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>c</t>
   </si>
@@ -101,6 +101,12 @@
     <t>最大法力值</t>
   </si>
   <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>闪避追加</t>
+  </si>
+  <si>
     <t>#直接使用没有加成的属性</t>
   </si>
   <si>
@@ -141,6 +147,9 @@
   </si>
   <si>
     <t>濒死状态</t>
+  </si>
+  <si>
+    <t>战斗随机数</t>
   </si>
 </sst>
 </file>
@@ -153,7 +162,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,12 +181,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF57A64A"/>
-      <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -649,137 +652,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -792,7 +795,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -862,7 +864,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1141,7 +1143,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H28"/>
+  <dimension ref="B2:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1383,55 +1385,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="1" t="s">
+    <row r="15" spans="3:8">
+      <c r="C15" s="3">
+        <v>1019</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="E15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="3:8">
       <c r="C16" s="3">
-        <v>3001</v>
+        <v>1020</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="3:8">
-      <c r="C17" s="3">
-        <v>3002</v>
-      </c>
-      <c r="D17" s="4" t="s">
+    <row r="17" spans="2:4">
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1</v>
-      </c>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" spans="3:8">
       <c r="C18" s="3">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>27</v>
@@ -1451,7 +1453,7 @@
     </row>
     <row r="19" spans="3:8">
       <c r="C19" s="3">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>28</v>
@@ -1471,53 +1473,53 @@
     </row>
     <row r="20" spans="3:8">
       <c r="C20" s="3">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="3:8">
       <c r="C21" s="3">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="3">
-        <v>5</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="3:8">
       <c r="C22" s="3">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1531,33 +1533,33 @@
     </row>
     <row r="23" spans="3:8">
       <c r="C23" s="3">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
+        <v>5</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:8">
       <c r="C24" s="3">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1571,7 +1573,7 @@
     </row>
     <row r="25" spans="3:8">
       <c r="C25" s="3">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>34</v>
@@ -1591,7 +1593,7 @@
     </row>
     <row r="26" spans="3:8">
       <c r="C26" s="3">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>35</v>
@@ -1611,7 +1613,7 @@
     </row>
     <row r="27" spans="3:8">
       <c r="C27" s="3">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>36</v>
@@ -1631,21 +1633,81 @@
     </row>
     <row r="28" spans="3:8">
       <c r="C28" s="3">
+        <v>3011</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8">
+      <c r="C29" s="3">
+        <v>3012</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8">
+      <c r="C30" s="3">
         <v>3013</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
+      <c r="D30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8">
+      <c r="C31" s="3">
+        <v>3014</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>c</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>战斗随机数</t>
+  </si>
+  <si>
+    <t>背包容量</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1146,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H31"/>
+  <dimension ref="B2:H32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1711,6 +1714,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32" spans="3:8">
+      <c r="C32" s="3">
+        <v>3015</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="3">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -1151,7 +1151,7 @@
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="11.875" style="1" customWidth="1"/>
     <col min="7" max="8" width="14.25" style="1" customWidth="1"/>

--- a/Excel/PlayerNumericConfig@cs.xlsx
+++ b/Excel/PlayerNumericConfig@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerNumericConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>c</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>背包容量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">精铁矿石 </t>
+  </si>
+  <si>
+    <t>皮革</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1152,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H32"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="21.125" style="1" customWidth="1"/>
@@ -1734,6 +1740,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="3">
+        <v>3016</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34" s="3">
+        <v>3017</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
